--- a/artfynd/A 7543-2024 artfynd.xlsx
+++ b/artfynd/A 7543-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117611499</v>
+        <v>117611479</v>
       </c>
       <c r="B2" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +804,7 @@
         <v>117612279</v>
       </c>
       <c r="B3" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 7543-2024 artfynd.xlsx
+++ b/artfynd/A 7543-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 7543-2024 artfynd.xlsx
+++ b/artfynd/A 7543-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117611499</v>
+        <v>117611479</v>
       </c>
       <c r="B2" t="n">
-        <v>100009</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,7 +720,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullmyran (Kullmyran), Gstr</t>
+          <t>Kullmyran, Kullmyran, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +799,7 @@
         <v>117612279</v>
       </c>
       <c r="B3" t="n">
-        <v>100009</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,7 +841,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullmyran (Kullmyran), Gstr</t>
+          <t>Kullmyran, Kullmyran, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">

--- a/artfynd/A 7543-2024 artfynd.xlsx
+++ b/artfynd/A 7543-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117611479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117612279</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>